--- a/Shared/XLS/SkillCard.xlsx
+++ b/Shared/XLS/SkillCard.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="6" r:id="rId1"/>
-    <sheet name="#SkillCard" sheetId="7" r:id="rId2"/>
-    <sheet name="#SkillCardUpgrade" sheetId="14" r:id="rId3"/>
+    <sheet name="#CardSkill" sheetId="7" r:id="rId2"/>
+    <sheet name="#CardSkillEnchant" sheetId="14" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -32,10 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -45,31 +45,27 @@
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCard</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -85,7 +81,7 @@
       </rPr>
       <t>ame</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -101,7 +97,7 @@
       </rPr>
       <t>esc</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -117,50 +113,39 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>GroupGrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_5</t>
-  </si>
-  <si>
-    <t>UltimateSkill</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!SkillInfo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -176,75 +161,140 @@
       </rPr>
       <t>kill_01</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Skill_1_Desc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCardUpgrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SourceGrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>TargetGrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>RequiredCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>SkillCardGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!SkillCardGrade</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>UltimateSkill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>BuyPrice_Ultimate</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SkillCard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Enchant</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -373,12 +423,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -392,17 +442,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -411,10 +461,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -691,7 +744,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -715,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -744,132 +797,172 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="15.375" style="2" customWidth="1"/>
-    <col min="7" max="8" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="15" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="6.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="19.25" style="2" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="2" customWidth="1"/>
+    <col min="11" max="12" width="13.375" style="2" customWidth="1"/>
+    <col min="13" max="14" width="15" style="2" customWidth="1"/>
+    <col min="15" max="16" width="17" style="2" customWidth="1"/>
+    <col min="17" max="17" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="19.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="19.25" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>9</v>
+      <c r="B1" s="14" t="s">
+        <v>34</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="N2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="11" t="s">
@@ -878,144 +971,179 @@
       <c r="G4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="H4" s="2">
+        <v>50</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2">
+        <v>100</v>
+      </c>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
       <c r="F11"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
       <c r="F12"/>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G19"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H19"/>
+    </row>
+    <row r="20" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G20"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H20"/>
+    </row>
+    <row r="21" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G21"/>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G22"/>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H22"/>
+    </row>
+    <row r="23" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G23"/>
-    </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H23"/>
+    </row>
+    <row r="24" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G24"/>
-    </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H24"/>
+    </row>
+    <row r="25" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G25"/>
-    </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H25"/>
+    </row>
+    <row r="26" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G26"/>
-    </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H26"/>
+    </row>
+    <row r="27" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G27"/>
-    </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H27"/>
+    </row>
+    <row r="28" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G28"/>
-    </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H28"/>
+    </row>
+    <row r="29" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G29"/>
-    </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H29"/>
+    </row>
+    <row r="30" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G30"/>
-    </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G31"/>
-    </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G32"/>
-    </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G33"/>
-    </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G34"/>
-    </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G35"/>
-    </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G36"/>
-    </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H36"/>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G37"/>
-    </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H37"/>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G38"/>
-    </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="H38"/>
+    </row>
+    <row r="39" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G39"/>
+      <c r="H39"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1042,10 +1170,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>28</v>
+        <v>23</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1059,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
@@ -1073,16 +1201,16 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -1098,10 +1226,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E4" s="11">
         <v>10</v>
@@ -1115,10 +1243,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E5" s="5">
         <v>15</v>
@@ -1132,10 +1260,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E6" s="5">
         <v>30</v>
@@ -1149,10 +1277,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E7" s="13">
         <v>50</v>
@@ -1203,7 +1331,7 @@
       <c r="G12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/SkillCard.xlsx
+++ b/Shared/XLS/SkillCard.xlsx
@@ -32,16 +32,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="117">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
-  </si>
-  <si>
-    <t>SKILL_PASSIVE_01</t>
   </si>
   <si>
     <t>Normal</t>
@@ -116,10 +113,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>GroupGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill_2</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -168,10 +161,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>SKILL_PASSIVE_02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>!Table</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -180,39 +169,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>TargetGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>RequiredCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Normal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Magic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SkillCardGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!SkillCardGrade</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -274,6 +231,513 @@
       </rPr>
       <t>Enchant</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_03</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_04</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_08</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_09</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kill_10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t/>
+    </r>
+  </si>
+  <si>
+    <t>Skill_2_Desc</t>
+  </si>
+  <si>
+    <t>Skill_3_Desc</t>
+  </si>
+  <si>
+    <t>Skill_4_Desc</t>
+  </si>
+  <si>
+    <t>Skill_5_Desc</t>
+  </si>
+  <si>
+    <t>Skill_6_Desc</t>
+  </si>
+  <si>
+    <t>Skill_7_Desc</t>
+  </si>
+  <si>
+    <t>Skill_8_Desc</t>
+  </si>
+  <si>
+    <t>Skill_9_Desc</t>
+  </si>
+  <si>
+    <t>Skill_10_Desc</t>
+  </si>
+  <si>
+    <t>skill_001</t>
+  </si>
+  <si>
+    <t>skill_002</t>
+  </si>
+  <si>
+    <t>skill_003</t>
+  </si>
+  <si>
+    <t>skill_004</t>
+  </si>
+  <si>
+    <t>skill_005</t>
+  </si>
+  <si>
+    <t>skill_006</t>
+  </si>
+  <si>
+    <t>skill_007</t>
+  </si>
+  <si>
+    <t>skill_008</t>
+  </si>
+  <si>
+    <t>skill_009</t>
+  </si>
+  <si>
+    <t>skill_010</t>
+  </si>
+  <si>
+    <t>SKILL_CARD_01_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_02_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_03_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_04_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_05_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_06_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_07_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_08_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_09_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_10_LV1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_01_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_02_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_03_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_04_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_05_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_06_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_07_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_08_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_09_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_10_LV2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_01_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_02_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_03_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_04_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_05_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_06_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_07_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_08_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_09_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_10_LV3</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_01_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_02_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_03_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_04_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_05_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_06_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_07_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_08_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_09_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_10_LV4</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_01_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_02_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_03_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_04_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_05_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_06_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_07_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_08_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_09_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SKILL_CARD_10_LV5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillGrade</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CardSkillGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>TargetLevel</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -768,32 +1232,32 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -810,13 +1274,16 @@
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.375" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="15.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.25" style="2" customWidth="1"/>
-    <col min="11" max="12" width="13.375" style="2" customWidth="1"/>
-    <col min="13" max="14" width="15" style="2" customWidth="1"/>
-    <col min="15" max="16" width="17" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="2" customWidth="1"/>
+    <col min="15" max="15" width="19.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17" style="2" customWidth="1"/>
     <col min="17" max="17" width="12.5" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.5" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="6.75" style="2" bestFit="1" customWidth="1"/>
@@ -830,10 +1297,10 @@
   <sheetData>
     <row r="1" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -846,106 +1313,106 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="J2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="H3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="L3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="V3" s="10"/>
       <c r="W3" s="10"/>
@@ -959,111 +1426,480 @@
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="F4" s="11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H4" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="J4" s="2">
-        <v>100</v>
-      </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L4" s="2">
+        <v>225</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N4" s="2">
+        <v>350</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="P4" s="2">
+        <v>525</v>
+      </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2">
+        <v>100</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J5" s="2">
+        <v>150</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L5" s="2">
+        <v>225</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N5" s="2">
+        <v>350</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="P5" s="2">
+        <v>525</v>
+      </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
+      <c r="B6" s="5">
+        <v>3</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="2">
+        <v>150</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="2">
+        <v>225</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="N6" s="2">
+        <v>350</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="P6" s="2">
+        <v>525</v>
+      </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
+      <c r="B7" s="13">
+        <v>4</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="2">
+        <v>100</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J7" s="2">
+        <v>150</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="L7" s="2">
+        <v>225</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="2">
+        <v>350</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P7" s="2">
+        <v>525</v>
+      </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
+      <c r="B8" s="13">
+        <v>5</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="11">
+        <v>200</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="2">
+        <v>300</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" s="2">
+        <v>450</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N8" s="2">
+        <v>675</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P8" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
+      <c r="B9" s="13">
+        <v>6</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="11">
+        <v>200</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="2">
+        <v>300</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="2">
+        <v>450</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N9" s="2">
+        <v>675</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="B10" s="13">
+        <v>7</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H10" s="2">
+        <v>300</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="J10" s="2">
+        <v>450</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L10" s="2">
+        <v>675</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="P10" s="2">
+        <v>1500</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="B11" s="13">
+        <v>8</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2">
+        <v>300</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="2">
+        <v>450</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="L11" s="2">
+        <v>675</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P11" s="2">
+        <v>1500</v>
+      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
+      <c r="B12" s="13">
+        <v>9</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2">
+        <v>400</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="2">
+        <v>600</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="2">
+        <v>900</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N12" s="2">
+        <v>1350</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P12" s="2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="2">
+        <v>600</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J13" s="2">
+        <v>900</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1350</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="P13" s="2">
+        <v>3000</v>
+      </c>
     </row>
     <row r="19" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G19"/>
       <c r="H19"/>
     </row>
     <row r="20" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G20"/>
       <c r="H20"/>
     </row>
     <row r="21" spans="7:8" x14ac:dyDescent="0.3">
@@ -1151,7 +1987,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
@@ -1170,10 +2006,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -1187,13 +2023,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
@@ -1201,16 +2037,16 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="7"/>
       <c r="B3" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -1226,13 +2062,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>28</v>
+        <v>2</v>
+      </c>
+      <c r="D4" s="11">
+        <v>1</v>
       </c>
       <c r="E4" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1243,16 +2079,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="5">
-        <v>15</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="D5" s="11">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11">
+        <v>2</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
@@ -1260,75 +2096,722 @@
         <v>3</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="5">
-        <v>30</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="D6" s="11">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11">
+        <v>4</v>
+      </c>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
-      <c r="B7" s="13">
+      <c r="B7" s="5">
         <v>4</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="13">
-        <v>50</v>
-      </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+        <v>2</v>
+      </c>
+      <c r="D7" s="11">
+        <v>4</v>
+      </c>
+      <c r="E7" s="11">
+        <v>8</v>
+      </c>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="B8" s="5">
+        <v>5</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="11">
+        <v>5</v>
+      </c>
+      <c r="E8" s="11">
+        <v>10</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="11">
+        <v>6</v>
+      </c>
+      <c r="E9" s="11">
+        <v>12</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B10"/>
-      <c r="C10"/>
-      <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="5">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11">
+        <v>14</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="5">
+        <v>8</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="11">
+        <v>8</v>
+      </c>
+      <c r="E11" s="11">
+        <v>16</v>
+      </c>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="5">
+        <v>9</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="11">
+        <v>9</v>
+      </c>
+      <c r="E12" s="11">
+        <v>18</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="5">
+        <v>10</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11">
+        <v>10</v>
+      </c>
+      <c r="E13" s="11">
+        <v>20</v>
+      </c>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="5">
+        <v>11</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5">
+        <v>12</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11">
+        <v>3</v>
+      </c>
+      <c r="E16" s="11">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="5">
+        <v>14</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="11">
+        <v>4</v>
+      </c>
+      <c r="E17" s="11">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="5">
+        <v>15</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11">
+        <v>5</v>
+      </c>
+      <c r="E18" s="11">
+        <v>10</v>
+      </c>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="5">
+        <v>16</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="11">
+        <v>6</v>
+      </c>
+      <c r="E19" s="11">
+        <v>12</v>
+      </c>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="5">
+        <v>17</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11">
+        <v>7</v>
+      </c>
+      <c r="E20" s="11">
+        <v>14</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="5">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11">
+        <v>8</v>
+      </c>
+      <c r="E21" s="11">
+        <v>16</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="5">
+        <v>19</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="11">
+        <v>9</v>
+      </c>
+      <c r="E22" s="11">
+        <v>18</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="5">
+        <v>20</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="11">
+        <v>10</v>
+      </c>
+      <c r="E23" s="11">
+        <v>20</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="5">
+        <v>21</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="11">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="5">
+        <v>22</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="11">
+        <v>2</v>
+      </c>
+      <c r="E25" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="5">
+        <v>23</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="11">
+        <v>3</v>
+      </c>
+      <c r="E26" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="5">
+        <v>24</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="11">
+        <v>4</v>
+      </c>
+      <c r="E27" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="5">
+        <v>25</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="11">
+        <v>5</v>
+      </c>
+      <c r="E28" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="5">
+        <v>26</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="11">
+        <v>6</v>
+      </c>
+      <c r="E29" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="5">
+        <v>27</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="11">
+        <v>7</v>
+      </c>
+      <c r="E30" s="11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B31" s="5">
+        <v>28</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="11">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B32" s="5">
+        <v>29</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="11">
+        <v>9</v>
+      </c>
+      <c r="E32" s="11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="5">
+        <v>30</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="11">
+        <v>10</v>
+      </c>
+      <c r="E33" s="11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="5">
+        <v>31</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="11">
+        <v>1</v>
+      </c>
+      <c r="E34" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="5">
+        <v>32</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="11">
+        <v>2</v>
+      </c>
+      <c r="E35" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="5">
+        <v>33</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="11">
+        <v>3</v>
+      </c>
+      <c r="E36" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="5">
+        <v>34</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="11">
+        <v>4</v>
+      </c>
+      <c r="E37" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="5">
+        <v>35</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="11">
+        <v>5</v>
+      </c>
+      <c r="E38" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="5">
+        <v>36</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="11">
+        <v>6</v>
+      </c>
+      <c r="E39" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="5">
+        <v>37</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="11">
+        <v>7</v>
+      </c>
+      <c r="E40" s="11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="5">
+        <v>38</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="11">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="5">
+        <v>39</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="11">
+        <v>9</v>
+      </c>
+      <c r="E42" s="11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B43" s="5">
+        <v>40</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="11">
+        <v>10</v>
+      </c>
+      <c r="E43" s="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B44" s="5">
+        <v>41</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" s="11">
+        <v>1</v>
+      </c>
+      <c r="E44" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B45" s="5">
+        <v>42</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="11">
+        <v>2</v>
+      </c>
+      <c r="E45" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B46" s="5">
+        <v>43</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="11">
+        <v>3</v>
+      </c>
+      <c r="E46" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B47" s="5">
+        <v>44</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="11">
+        <v>4</v>
+      </c>
+      <c r="E47" s="11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B48" s="5">
+        <v>45</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="11">
+        <v>5</v>
+      </c>
+      <c r="E48" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="5">
+        <v>46</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="11">
+        <v>6</v>
+      </c>
+      <c r="E49" s="11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="5">
+        <v>47</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="11">
+        <v>7</v>
+      </c>
+      <c r="E50" s="11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="5">
+        <v>48</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="11">
+        <v>8</v>
+      </c>
+      <c r="E51" s="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="5">
+        <v>49</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="11">
+        <v>9</v>
+      </c>
+      <c r="E52" s="11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="5">
+        <v>50</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="11">
+        <v>10</v>
+      </c>
+      <c r="E53" s="11">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
